--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20261019.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20261019.xlsx
@@ -1657,17 +1657,17 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>8422</t>
+          <t>5536</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>可寧衛股</t>
+          <t>聖暉工程</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>54,146,000</t>
+          <t>1,720,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -1679,17 +1679,17 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>5536</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>聖暉工程</t>
+          <t>可寧衛股</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>1,720,000</t>
+          <t>54,146,000</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
